--- a/case_studies/2030/technologies.xlsx
+++ b/case_studies/2030/technologies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\case_studies\2030\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC0F1109-5BE6-43E3-B4F8-101898264FF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{173884FA-8233-44E3-8672-A6354D1472BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="existing" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="38">
   <si>
     <t>cluster</t>
   </si>
@@ -120,6 +120,21 @@
   </si>
   <si>
     <t>NL4</t>
+  </si>
+  <si>
+    <t>electricity_grid_connection_BE</t>
+  </si>
+  <si>
+    <t>electricity_grid_connection_DE</t>
+  </si>
+  <si>
+    <t>electricity_grid_connection_NL</t>
+  </si>
+  <si>
+    <t>H2_network_connection_in</t>
+  </si>
+  <si>
+    <t>H2_network_connection_out</t>
   </si>
 </sst>
 </file>
@@ -171,7 +186,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -194,11 +209,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -213,6 +239,15 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -517,7 +552,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z8"/>
+  <dimension ref="A1:AE8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -546,7 +581,7 @@
     <col min="25" max="26" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -625,8 +660,23 @@
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="AA1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD1" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE1" s="6" t="s">
+        <v>37</v>
+      </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>26</v>
       </c>
@@ -705,8 +755,23 @@
       <c r="Z2" s="3">
         <v>13.37</v>
       </c>
+      <c r="AA2" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="7">
+        <v>1</v>
+      </c>
+      <c r="AE2" s="7">
+        <v>1</v>
+      </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>27</v>
       </c>
@@ -785,8 +850,23 @@
       <c r="Z3" s="5">
         <v>0</v>
       </c>
+      <c r="AA3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="8">
+        <v>1</v>
+      </c>
+      <c r="AE3" s="8">
+        <v>1</v>
+      </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>28</v>
       </c>
@@ -865,8 +945,23 @@
       <c r="Z4" s="3">
         <v>4.21</v>
       </c>
+      <c r="AA4" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="7">
+        <v>1</v>
+      </c>
+      <c r="AE4" s="7">
+        <v>1</v>
+      </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>29</v>
       </c>
@@ -945,8 +1040,23 @@
       <c r="Z5" s="5">
         <v>0</v>
       </c>
+      <c r="AA5" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="8">
+        <v>1</v>
+      </c>
+      <c r="AE5" s="8">
+        <v>1</v>
+      </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>30</v>
       </c>
@@ -1025,8 +1135,23 @@
       <c r="Z6" s="3">
         <v>0.1</v>
       </c>
+      <c r="AA6" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="7">
+        <v>1</v>
+      </c>
+      <c r="AE6" s="7">
+        <v>1</v>
+      </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>31</v>
       </c>
@@ -1105,8 +1230,23 @@
       <c r="Z7" s="5">
         <v>0</v>
       </c>
+      <c r="AA7" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="8">
+        <v>1</v>
+      </c>
+      <c r="AE7" s="8">
+        <v>1</v>
+      </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>32</v>
       </c>
@@ -1184,6 +1324,21 @@
       </c>
       <c r="Z8" s="3">
         <v>0.28999999999999998</v>
+      </c>
+      <c r="AA8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="7">
+        <v>1</v>
+      </c>
+      <c r="AE8" s="7">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1193,7 +1348,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{590A44D7-82AE-472B-8B5E-1B52016CA01D}">
-  <dimension ref="A1:Z8"/>
+  <dimension ref="A1:AE8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1222,7 +1377,7 @@
     <col min="25" max="26" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1301,8 +1456,23 @@
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="AA1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD1" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE1" s="6" t="s">
+        <v>37</v>
+      </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>26</v>
       </c>
@@ -1381,8 +1551,23 @@
       <c r="Z2" s="3">
         <v>1</v>
       </c>
+      <c r="AA2" s="3">
+        <v>1</v>
+      </c>
+      <c r="AB2" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="7">
+        <v>1</v>
+      </c>
+      <c r="AE2" s="7">
+        <v>1</v>
+      </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>27</v>
       </c>
@@ -1461,8 +1646,23 @@
       <c r="Z3" s="5">
         <v>1</v>
       </c>
+      <c r="AA3" s="5">
+        <v>1</v>
+      </c>
+      <c r="AB3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="8">
+        <v>1</v>
+      </c>
+      <c r="AE3" s="8">
+        <v>1</v>
+      </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>28</v>
       </c>
@@ -1541,8 +1741,23 @@
       <c r="Z4" s="3">
         <v>1</v>
       </c>
+      <c r="AA4" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC4" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="7">
+        <v>1</v>
+      </c>
+      <c r="AE4" s="7">
+        <v>1</v>
+      </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>29</v>
       </c>
@@ -1621,8 +1836,23 @@
       <c r="Z5" s="5">
         <v>1</v>
       </c>
+      <c r="AA5" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="5">
+        <v>1</v>
+      </c>
+      <c r="AD5" s="8">
+        <v>1</v>
+      </c>
+      <c r="AE5" s="8">
+        <v>1</v>
+      </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>30</v>
       </c>
@@ -1701,8 +1931,23 @@
       <c r="Z6" s="3">
         <v>1</v>
       </c>
+      <c r="AA6" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="3">
+        <v>1</v>
+      </c>
+      <c r="AD6" s="7">
+        <v>1</v>
+      </c>
+      <c r="AE6" s="7">
+        <v>1</v>
+      </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>31</v>
       </c>
@@ -1781,8 +2026,23 @@
       <c r="Z7" s="5">
         <v>1</v>
       </c>
+      <c r="AA7" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="5">
+        <v>1</v>
+      </c>
+      <c r="AD7" s="8">
+        <v>1</v>
+      </c>
+      <c r="AE7" s="8">
+        <v>1</v>
+      </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>32</v>
       </c>
@@ -1859,6 +2119,21 @@
         <v>1</v>
       </c>
       <c r="Z8" s="3">
+        <v>1</v>
+      </c>
+      <c r="AA8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="3">
+        <v>1</v>
+      </c>
+      <c r="AD8" s="7">
+        <v>1</v>
+      </c>
+      <c r="AE8" s="7">
         <v>1</v>
       </c>
     </row>

--- a/case_studies/2030/technologies.xlsx
+++ b/case_studies/2030/technologies.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\case_studies\2030\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{173884FA-8233-44E3-8672-A6354D1472BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{360F88A8-F9A4-4365-8DA3-AC4E9778DEEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -552,7 +552,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AE8"/>
+  <dimension ref="A1:AE9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -765,10 +765,10 @@
         <v>0</v>
       </c>
       <c r="AD2" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE2" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.3">
@@ -860,10 +860,10 @@
         <v>0</v>
       </c>
       <c r="AD3" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE3" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.3">
@@ -955,10 +955,10 @@
         <v>0</v>
       </c>
       <c r="AD4" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE4" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.3">
@@ -1050,10 +1050,10 @@
         <v>0</v>
       </c>
       <c r="AD5" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE5" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.3">
@@ -1145,10 +1145,10 @@
         <v>0</v>
       </c>
       <c r="AD6" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE6" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.3">
@@ -1240,10 +1240,10 @@
         <v>0</v>
       </c>
       <c r="AD7" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE7" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.3">
@@ -1335,11 +1335,14 @@
         <v>0</v>
       </c>
       <c r="AD8" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE8" s="7">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="AE9" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/case_studies/2030/technologies.xlsx
+++ b/case_studies/2030/technologies.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{360F88A8-F9A4-4365-8DA3-AC4E9778DEEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="existing" sheetId="1" r:id="rId1"/>
@@ -553,7 +553,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AE9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="3" width="10" customWidth="1"/>
@@ -581,7 +581,7 @@
     <col min="25" max="26" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -676,7 +676,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>26</v>
       </c>
@@ -771,7 +771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>27</v>
       </c>
@@ -866,7 +866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>28</v>
       </c>
@@ -961,7 +961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>29</v>
       </c>
@@ -1056,7 +1056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>30</v>
       </c>
@@ -1151,7 +1151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>31</v>
       </c>
@@ -1246,7 +1246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>32</v>
       </c>
@@ -1341,7 +1341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
       <c r="AE9" s="8"/>
     </row>
   </sheetData>
@@ -1352,7 +1352,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{590A44D7-82AE-472B-8B5E-1B52016CA01D}">
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="3" width="10" customWidth="1"/>
@@ -1380,7 +1380,7 @@
     <col min="25" max="26" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1475,7 +1475,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>26</v>
       </c>
@@ -1570,7 +1570,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>27</v>
       </c>
@@ -1665,7 +1665,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>28</v>
       </c>
@@ -1760,7 +1760,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>29</v>
       </c>
@@ -1855,7 +1855,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>30</v>
       </c>
@@ -1950,7 +1950,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>31</v>
       </c>
@@ -2045,7 +2045,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>32</v>
       </c>

--- a/case_studies/2030/technologies.xlsx
+++ b/case_studies/2030/technologies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\case_studies\2030\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{360F88A8-F9A4-4365-8DA3-AC4E9778DEEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B66526CB-7E87-44C4-AB9C-7C03BAFCE5A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="existing" sheetId="1" r:id="rId1"/>
@@ -101,6 +101,21 @@
     <t>CO2toEmissions</t>
   </si>
   <si>
+    <t>electricity_grid_connection_BE</t>
+  </si>
+  <si>
+    <t>electricity_grid_connection_DE</t>
+  </si>
+  <si>
+    <t>electricity_grid_connection_NL</t>
+  </si>
+  <si>
+    <t>H2_network_connection_in</t>
+  </si>
+  <si>
+    <t>H2_network_connection_out</t>
+  </si>
+  <si>
     <t>BEL1</t>
   </si>
   <si>
@@ -120,21 +135,6 @@
   </si>
   <si>
     <t>NL4</t>
-  </si>
-  <si>
-    <t>electricity_grid_connection_BE</t>
-  </si>
-  <si>
-    <t>electricity_grid_connection_DE</t>
-  </si>
-  <si>
-    <t>electricity_grid_connection_NL</t>
-  </si>
-  <si>
-    <t>H2_network_connection_in</t>
-  </si>
-  <si>
-    <t>H2_network_connection_out</t>
   </si>
 </sst>
 </file>
@@ -186,7 +186,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -209,22 +209,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -239,15 +228,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -552,8 +532,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AE9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AE8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="3" width="10" customWidth="1"/>
@@ -579,9 +559,12 @@
     <col min="23" max="23" width="11" customWidth="1"/>
     <col min="24" max="24" width="15" customWidth="1"/>
     <col min="25" max="26" width="16" customWidth="1"/>
+    <col min="27" max="29" width="32" customWidth="1"/>
+    <col min="30" max="30" width="26" customWidth="1"/>
+    <col min="31" max="31" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -661,24 +644,24 @@
         <v>25</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD1" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="AE1" s="6" t="s">
-        <v>37</v>
+        <v>28</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B2" s="3">
         <v>0</v>
@@ -764,16 +747,16 @@
       <c r="AC2" s="3">
         <v>0</v>
       </c>
-      <c r="AD2" s="7">
-        <v>0</v>
-      </c>
-      <c r="AE2" s="7">
+      <c r="AD2" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B3" s="5">
         <v>0</v>
@@ -859,16 +842,16 @@
       <c r="AC3" s="5">
         <v>0</v>
       </c>
-      <c r="AD3" s="8">
-        <v>0</v>
-      </c>
-      <c r="AE3" s="8">
+      <c r="AD3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
@@ -892,10 +875,10 @@
         <v>0</v>
       </c>
       <c r="I4" s="3">
-        <v>0</v>
+        <v>39.630000000000003</v>
       </c>
       <c r="J4" s="3">
-        <v>0</v>
+        <v>39.54</v>
       </c>
       <c r="K4" s="3">
         <v>0</v>
@@ -913,10 +896,10 @@
         <v>0</v>
       </c>
       <c r="P4" s="3">
-        <v>0</v>
+        <v>79.28</v>
       </c>
       <c r="Q4" s="3">
-        <v>60.64</v>
+        <v>147.93</v>
       </c>
       <c r="R4" s="3">
         <v>0</v>
@@ -954,16 +937,16 @@
       <c r="AC4" s="3">
         <v>0</v>
       </c>
-      <c r="AD4" s="7">
-        <v>0</v>
-      </c>
-      <c r="AE4" s="7">
+      <c r="AD4" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B5" s="5">
         <v>0</v>
@@ -984,13 +967,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="5">
-        <v>0.53</v>
+        <v>0</v>
       </c>
       <c r="I5" s="5">
-        <v>0</v>
+        <v>29.96</v>
       </c>
       <c r="J5" s="5">
-        <v>0</v>
+        <v>28.15</v>
       </c>
       <c r="K5" s="5">
         <v>0</v>
@@ -1008,25 +991,25 @@
         <v>0</v>
       </c>
       <c r="P5" s="5">
-        <v>0</v>
+        <v>65.2</v>
       </c>
       <c r="Q5" s="5">
-        <v>0</v>
+        <v>84.4</v>
       </c>
       <c r="R5" s="5">
         <v>0</v>
       </c>
       <c r="S5" s="5">
-        <v>0</v>
+        <v>12.99</v>
       </c>
       <c r="T5" s="5">
-        <v>0</v>
+        <v>29.96</v>
       </c>
       <c r="U5" s="5">
         <v>0</v>
       </c>
       <c r="V5" s="5">
-        <v>0</v>
+        <v>0.36</v>
       </c>
       <c r="W5" s="5">
         <v>0</v>
@@ -1038,7 +1021,7 @@
         <v>0</v>
       </c>
       <c r="Z5" s="5">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AA5" s="5">
         <v>0</v>
@@ -1049,16 +1032,16 @@
       <c r="AC5" s="5">
         <v>0</v>
       </c>
-      <c r="AD5" s="8">
-        <v>0</v>
-      </c>
-      <c r="AE5" s="8">
+      <c r="AD5" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
@@ -1082,10 +1065,10 @@
         <v>0</v>
       </c>
       <c r="I6" s="3">
-        <v>26.73</v>
+        <v>60.08</v>
       </c>
       <c r="J6" s="3">
-        <v>25.38</v>
+        <v>59.46</v>
       </c>
       <c r="K6" s="3">
         <v>0</v>
@@ -1103,10 +1086,10 @@
         <v>0</v>
       </c>
       <c r="P6" s="3">
-        <v>53.46</v>
+        <v>120.16</v>
       </c>
       <c r="Q6" s="3">
-        <v>72.67</v>
+        <v>139.37</v>
       </c>
       <c r="R6" s="3">
         <v>0</v>
@@ -1115,7 +1098,7 @@
         <v>12.99</v>
       </c>
       <c r="T6" s="3">
-        <v>0</v>
+        <v>28.42</v>
       </c>
       <c r="U6" s="3">
         <v>0</v>
@@ -1144,16 +1127,16 @@
       <c r="AC6" s="3">
         <v>0</v>
       </c>
-      <c r="AD6" s="7">
-        <v>0</v>
-      </c>
-      <c r="AE6" s="7">
+      <c r="AD6" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B7" s="5">
         <v>0</v>
@@ -1239,16 +1222,16 @@
       <c r="AC7" s="5">
         <v>0</v>
       </c>
-      <c r="AD7" s="8">
-        <v>0</v>
-      </c>
-      <c r="AE7" s="8">
+      <c r="AD7" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="5">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
@@ -1272,10 +1255,10 @@
         <v>0</v>
       </c>
       <c r="I8" s="3">
-        <v>28.78</v>
+        <v>142.69</v>
       </c>
       <c r="J8" s="3">
-        <v>23.62</v>
+        <v>141.94</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -1293,25 +1276,25 @@
         <v>0</v>
       </c>
       <c r="P8" s="3">
-        <v>57.55</v>
+        <v>285.38</v>
       </c>
       <c r="Q8" s="3">
-        <v>115.16</v>
+        <v>323.79000000000002</v>
       </c>
       <c r="R8" s="3">
         <v>0</v>
       </c>
       <c r="S8" s="3">
-        <v>38.950000000000003</v>
+        <v>25.97</v>
       </c>
       <c r="T8" s="3">
-        <v>0</v>
+        <v>106.11</v>
       </c>
       <c r="U8" s="3">
         <v>0</v>
       </c>
       <c r="V8" s="3">
-        <v>1.07</v>
+        <v>0.72</v>
       </c>
       <c r="W8" s="3">
         <v>0</v>
@@ -1323,7 +1306,7 @@
         <v>0</v>
       </c>
       <c r="Z8" s="3">
-        <v>0.28999999999999998</v>
+        <v>0.19</v>
       </c>
       <c r="AA8" s="3">
         <v>0</v>
@@ -1334,15 +1317,12 @@
       <c r="AC8" s="3">
         <v>0</v>
       </c>
-      <c r="AD8" s="7">
-        <v>0</v>
-      </c>
-      <c r="AE8" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="AE9" s="8"/>
+      <c r="AD8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="3">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1350,9 +1330,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{590A44D7-82AE-472B-8B5E-1B52016CA01D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F5AD1E0-8508-49B7-9592-771F18E2972C}">
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="3" width="10" customWidth="1"/>
@@ -1378,9 +1358,12 @@
     <col min="23" max="23" width="11" customWidth="1"/>
     <col min="24" max="24" width="15" customWidth="1"/>
     <col min="25" max="26" width="16" customWidth="1"/>
+    <col min="27" max="29" width="32" customWidth="1"/>
+    <col min="30" max="30" width="26" customWidth="1"/>
+    <col min="31" max="31" width="27" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1460,595 +1443,595 @@
         <v>25</v>
       </c>
       <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="3">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3">
+        <v>1</v>
+      </c>
+      <c r="E2" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2" s="3">
+        <v>1</v>
+      </c>
+      <c r="G2" s="3">
+        <v>1</v>
+      </c>
+      <c r="H2" s="3">
+        <v>1</v>
+      </c>
+      <c r="I2" s="3">
+        <v>1</v>
+      </c>
+      <c r="J2" s="3">
+        <v>1</v>
+      </c>
+      <c r="K2" s="3">
+        <v>1</v>
+      </c>
+      <c r="L2" s="3">
+        <v>1</v>
+      </c>
+      <c r="M2" s="3">
+        <v>1</v>
+      </c>
+      <c r="N2" s="3">
+        <v>1</v>
+      </c>
+      <c r="O2" s="3">
+        <v>1</v>
+      </c>
+      <c r="P2" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="3">
+        <v>1</v>
+      </c>
+      <c r="R2" s="3">
+        <v>1</v>
+      </c>
+      <c r="S2" s="3">
+        <v>1</v>
+      </c>
+      <c r="T2" s="3">
+        <v>1</v>
+      </c>
+      <c r="U2" s="3">
+        <v>1</v>
+      </c>
+      <c r="V2" s="3">
+        <v>1</v>
+      </c>
+      <c r="W2" s="3">
+        <v>1</v>
+      </c>
+      <c r="X2" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y2" s="3">
+        <v>1</v>
+      </c>
+      <c r="Z2" s="3">
+        <v>1</v>
+      </c>
+      <c r="AA2" s="3">
+        <v>1</v>
+      </c>
+      <c r="AB2" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="3">
+        <v>1</v>
+      </c>
+      <c r="AE2" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="5">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5">
+        <v>1</v>
+      </c>
+      <c r="E3" s="5">
+        <v>1</v>
+      </c>
+      <c r="F3" s="5">
+        <v>1</v>
+      </c>
+      <c r="G3" s="5">
+        <v>1</v>
+      </c>
+      <c r="H3" s="5">
+        <v>1</v>
+      </c>
+      <c r="I3" s="5">
+        <v>1</v>
+      </c>
+      <c r="J3" s="5">
+        <v>1</v>
+      </c>
+      <c r="K3" s="5">
+        <v>1</v>
+      </c>
+      <c r="L3" s="5">
+        <v>1</v>
+      </c>
+      <c r="M3" s="5">
+        <v>1</v>
+      </c>
+      <c r="N3" s="5">
+        <v>1</v>
+      </c>
+      <c r="O3" s="5">
+        <v>1</v>
+      </c>
+      <c r="P3" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="5">
+        <v>1</v>
+      </c>
+      <c r="R3" s="5">
+        <v>1</v>
+      </c>
+      <c r="S3" s="5">
+        <v>1</v>
+      </c>
+      <c r="T3" s="5">
+        <v>1</v>
+      </c>
+      <c r="U3" s="5">
+        <v>1</v>
+      </c>
+      <c r="V3" s="5">
+        <v>1</v>
+      </c>
+      <c r="W3" s="5">
+        <v>1</v>
+      </c>
+      <c r="X3" s="5">
+        <v>1</v>
+      </c>
+      <c r="Y3" s="5">
+        <v>1</v>
+      </c>
+      <c r="Z3" s="5">
+        <v>1</v>
+      </c>
+      <c r="AA3" s="5">
+        <v>1</v>
+      </c>
+      <c r="AB3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="5">
+        <v>1</v>
+      </c>
+      <c r="AE3" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="B4" s="3">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3">
+        <v>1</v>
+      </c>
+      <c r="F4" s="3">
+        <v>1</v>
+      </c>
+      <c r="G4" s="3">
+        <v>1</v>
+      </c>
+      <c r="H4" s="3">
+        <v>1</v>
+      </c>
+      <c r="I4" s="3">
+        <v>1</v>
+      </c>
+      <c r="J4" s="3">
+        <v>1</v>
+      </c>
+      <c r="K4" s="3">
+        <v>1</v>
+      </c>
+      <c r="L4" s="3">
+        <v>1</v>
+      </c>
+      <c r="M4" s="3">
+        <v>1</v>
+      </c>
+      <c r="N4" s="3">
+        <v>1</v>
+      </c>
+      <c r="O4" s="3">
+        <v>1</v>
+      </c>
+      <c r="P4" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="3">
+        <v>1</v>
+      </c>
+      <c r="R4" s="3">
+        <v>1</v>
+      </c>
+      <c r="S4" s="3">
+        <v>1</v>
+      </c>
+      <c r="T4" s="3">
+        <v>1</v>
+      </c>
+      <c r="U4" s="3">
+        <v>1</v>
+      </c>
+      <c r="V4" s="3">
+        <v>1</v>
+      </c>
+      <c r="W4" s="3">
+        <v>1</v>
+      </c>
+      <c r="X4" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y4" s="3">
+        <v>1</v>
+      </c>
+      <c r="Z4" s="3">
+        <v>1</v>
+      </c>
+      <c r="AA4" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC4" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="3">
+        <v>1</v>
+      </c>
+      <c r="AE4" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="B5" s="5">
+        <v>1</v>
+      </c>
+      <c r="C5" s="5">
+        <v>1</v>
+      </c>
+      <c r="D5" s="5">
+        <v>1</v>
+      </c>
+      <c r="E5" s="5">
+        <v>1</v>
+      </c>
+      <c r="F5" s="5">
+        <v>1</v>
+      </c>
+      <c r="G5" s="5">
+        <v>1</v>
+      </c>
+      <c r="H5" s="5">
+        <v>1</v>
+      </c>
+      <c r="I5" s="5">
+        <v>1</v>
+      </c>
+      <c r="J5" s="5">
+        <v>1</v>
+      </c>
+      <c r="K5" s="5">
+        <v>1</v>
+      </c>
+      <c r="L5" s="5">
+        <v>1</v>
+      </c>
+      <c r="M5" s="5">
+        <v>1</v>
+      </c>
+      <c r="N5" s="5">
+        <v>1</v>
+      </c>
+      <c r="O5" s="5">
+        <v>1</v>
+      </c>
+      <c r="P5" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="5">
+        <v>1</v>
+      </c>
+      <c r="R5" s="5">
+        <v>1</v>
+      </c>
+      <c r="S5" s="5">
+        <v>1</v>
+      </c>
+      <c r="T5" s="5">
+        <v>1</v>
+      </c>
+      <c r="U5" s="5">
+        <v>1</v>
+      </c>
+      <c r="V5" s="5">
+        <v>1</v>
+      </c>
+      <c r="W5" s="5">
+        <v>1</v>
+      </c>
+      <c r="X5" s="5">
+        <v>1</v>
+      </c>
+      <c r="Y5" s="5">
+        <v>1</v>
+      </c>
+      <c r="Z5" s="5">
+        <v>1</v>
+      </c>
+      <c r="AA5" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="5">
+        <v>1</v>
+      </c>
+      <c r="AD5" s="5">
+        <v>1</v>
+      </c>
+      <c r="AE5" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AD1" s="6" t="s">
+      <c r="B6" s="3">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3">
+        <v>1</v>
+      </c>
+      <c r="D6" s="3">
+        <v>1</v>
+      </c>
+      <c r="E6" s="3">
+        <v>1</v>
+      </c>
+      <c r="F6" s="3">
+        <v>1</v>
+      </c>
+      <c r="G6" s="3">
+        <v>1</v>
+      </c>
+      <c r="H6" s="3">
+        <v>1</v>
+      </c>
+      <c r="I6" s="3">
+        <v>1</v>
+      </c>
+      <c r="J6" s="3">
+        <v>1</v>
+      </c>
+      <c r="K6" s="3">
+        <v>1</v>
+      </c>
+      <c r="L6" s="3">
+        <v>1</v>
+      </c>
+      <c r="M6" s="3">
+        <v>1</v>
+      </c>
+      <c r="N6" s="3">
+        <v>1</v>
+      </c>
+      <c r="O6" s="3">
+        <v>1</v>
+      </c>
+      <c r="P6" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="3">
+        <v>1</v>
+      </c>
+      <c r="R6" s="3">
+        <v>1</v>
+      </c>
+      <c r="S6" s="3">
+        <v>1</v>
+      </c>
+      <c r="T6" s="3">
+        <v>1</v>
+      </c>
+      <c r="U6" s="3">
+        <v>1</v>
+      </c>
+      <c r="V6" s="3">
+        <v>1</v>
+      </c>
+      <c r="W6" s="3">
+        <v>1</v>
+      </c>
+      <c r="X6" s="3">
+        <v>1</v>
+      </c>
+      <c r="Y6" s="3">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="3">
+        <v>1</v>
+      </c>
+      <c r="AA6" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="3">
+        <v>1</v>
+      </c>
+      <c r="AD6" s="3">
+        <v>1</v>
+      </c>
+      <c r="AE6" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="AE1" s="6" t="s">
+      <c r="B7" s="5">
+        <v>1</v>
+      </c>
+      <c r="C7" s="5">
+        <v>1</v>
+      </c>
+      <c r="D7" s="5">
+        <v>1</v>
+      </c>
+      <c r="E7" s="5">
+        <v>1</v>
+      </c>
+      <c r="F7" s="5">
+        <v>1</v>
+      </c>
+      <c r="G7" s="5">
+        <v>1</v>
+      </c>
+      <c r="H7" s="5">
+        <v>1</v>
+      </c>
+      <c r="I7" s="5">
+        <v>1</v>
+      </c>
+      <c r="J7" s="5">
+        <v>1</v>
+      </c>
+      <c r="K7" s="5">
+        <v>1</v>
+      </c>
+      <c r="L7" s="5">
+        <v>1</v>
+      </c>
+      <c r="M7" s="5">
+        <v>1</v>
+      </c>
+      <c r="N7" s="5">
+        <v>1</v>
+      </c>
+      <c r="O7" s="5">
+        <v>1</v>
+      </c>
+      <c r="P7" s="5">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="5">
+        <v>1</v>
+      </c>
+      <c r="R7" s="5">
+        <v>1</v>
+      </c>
+      <c r="S7" s="5">
+        <v>1</v>
+      </c>
+      <c r="T7" s="5">
+        <v>1</v>
+      </c>
+      <c r="U7" s="5">
+        <v>1</v>
+      </c>
+      <c r="V7" s="5">
+        <v>1</v>
+      </c>
+      <c r="W7" s="5">
+        <v>1</v>
+      </c>
+      <c r="X7" s="5">
+        <v>1</v>
+      </c>
+      <c r="Y7" s="5">
+        <v>1</v>
+      </c>
+      <c r="Z7" s="5">
+        <v>1</v>
+      </c>
+      <c r="AA7" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="5">
+        <v>1</v>
+      </c>
+      <c r="AD7" s="5">
+        <v>1</v>
+      </c>
+      <c r="AE7" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B2" s="3">
-        <v>1</v>
-      </c>
-      <c r="C2" s="3">
-        <v>1</v>
-      </c>
-      <c r="D2" s="3">
-        <v>1</v>
-      </c>
-      <c r="E2" s="3">
-        <v>1</v>
-      </c>
-      <c r="F2" s="3">
-        <v>1</v>
-      </c>
-      <c r="G2" s="3">
-        <v>1</v>
-      </c>
-      <c r="H2" s="3">
-        <v>1</v>
-      </c>
-      <c r="I2" s="3">
-        <v>1</v>
-      </c>
-      <c r="J2" s="3">
-        <v>1</v>
-      </c>
-      <c r="K2" s="3">
-        <v>1</v>
-      </c>
-      <c r="L2" s="3">
-        <v>1</v>
-      </c>
-      <c r="M2" s="3">
-        <v>1</v>
-      </c>
-      <c r="N2" s="3">
-        <v>1</v>
-      </c>
-      <c r="O2" s="3">
-        <v>1</v>
-      </c>
-      <c r="P2" s="3">
-        <v>1</v>
-      </c>
-      <c r="Q2" s="3">
-        <v>1</v>
-      </c>
-      <c r="R2" s="3">
-        <v>1</v>
-      </c>
-      <c r="S2" s="3">
-        <v>1</v>
-      </c>
-      <c r="T2" s="3">
-        <v>1</v>
-      </c>
-      <c r="U2" s="3">
-        <v>1</v>
-      </c>
-      <c r="V2" s="3">
-        <v>1</v>
-      </c>
-      <c r="W2" s="3">
-        <v>1</v>
-      </c>
-      <c r="X2" s="3">
-        <v>1</v>
-      </c>
-      <c r="Y2" s="3">
-        <v>1</v>
-      </c>
-      <c r="Z2" s="3">
-        <v>1</v>
-      </c>
-      <c r="AA2" s="3">
-        <v>1</v>
-      </c>
-      <c r="AB2" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC2" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD2" s="7">
-        <v>1</v>
-      </c>
-      <c r="AE2" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B3" s="5">
-        <v>1</v>
-      </c>
-      <c r="C3" s="5">
-        <v>1</v>
-      </c>
-      <c r="D3" s="5">
-        <v>1</v>
-      </c>
-      <c r="E3" s="5">
-        <v>1</v>
-      </c>
-      <c r="F3" s="5">
-        <v>1</v>
-      </c>
-      <c r="G3" s="5">
-        <v>1</v>
-      </c>
-      <c r="H3" s="5">
-        <v>1</v>
-      </c>
-      <c r="I3" s="5">
-        <v>1</v>
-      </c>
-      <c r="J3" s="5">
-        <v>1</v>
-      </c>
-      <c r="K3" s="5">
-        <v>1</v>
-      </c>
-      <c r="L3" s="5">
-        <v>1</v>
-      </c>
-      <c r="M3" s="5">
-        <v>1</v>
-      </c>
-      <c r="N3" s="5">
-        <v>1</v>
-      </c>
-      <c r="O3" s="5">
-        <v>1</v>
-      </c>
-      <c r="P3" s="5">
-        <v>1</v>
-      </c>
-      <c r="Q3" s="5">
-        <v>1</v>
-      </c>
-      <c r="R3" s="5">
-        <v>1</v>
-      </c>
-      <c r="S3" s="5">
-        <v>1</v>
-      </c>
-      <c r="T3" s="5">
-        <v>1</v>
-      </c>
-      <c r="U3" s="5">
-        <v>1</v>
-      </c>
-      <c r="V3" s="5">
-        <v>1</v>
-      </c>
-      <c r="W3" s="5">
-        <v>1</v>
-      </c>
-      <c r="X3" s="5">
-        <v>1</v>
-      </c>
-      <c r="Y3" s="5">
-        <v>1</v>
-      </c>
-      <c r="Z3" s="5">
-        <v>1</v>
-      </c>
-      <c r="AA3" s="5">
-        <v>1</v>
-      </c>
-      <c r="AB3" s="5">
-        <v>0</v>
-      </c>
-      <c r="AC3" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD3" s="8">
-        <v>1</v>
-      </c>
-      <c r="AE3" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" s="3">
-        <v>1</v>
-      </c>
-      <c r="C4" s="3">
-        <v>1</v>
-      </c>
-      <c r="D4" s="3">
-        <v>1</v>
-      </c>
-      <c r="E4" s="3">
-        <v>1</v>
-      </c>
-      <c r="F4" s="3">
-        <v>1</v>
-      </c>
-      <c r="G4" s="3">
-        <v>1</v>
-      </c>
-      <c r="H4" s="3">
-        <v>1</v>
-      </c>
-      <c r="I4" s="3">
-        <v>1</v>
-      </c>
-      <c r="J4" s="3">
-        <v>1</v>
-      </c>
-      <c r="K4" s="3">
-        <v>1</v>
-      </c>
-      <c r="L4" s="3">
-        <v>1</v>
-      </c>
-      <c r="M4" s="3">
-        <v>1</v>
-      </c>
-      <c r="N4" s="3">
-        <v>1</v>
-      </c>
-      <c r="O4" s="3">
-        <v>1</v>
-      </c>
-      <c r="P4" s="3">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="3">
-        <v>1</v>
-      </c>
-      <c r="R4" s="3">
-        <v>1</v>
-      </c>
-      <c r="S4" s="3">
-        <v>1</v>
-      </c>
-      <c r="T4" s="3">
-        <v>1</v>
-      </c>
-      <c r="U4" s="3">
-        <v>1</v>
-      </c>
-      <c r="V4" s="3">
-        <v>1</v>
-      </c>
-      <c r="W4" s="3">
-        <v>1</v>
-      </c>
-      <c r="X4" s="3">
-        <v>1</v>
-      </c>
-      <c r="Y4" s="3">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="3">
-        <v>1</v>
-      </c>
-      <c r="AA4" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB4" s="3">
-        <v>1</v>
-      </c>
-      <c r="AC4" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD4" s="7">
-        <v>1</v>
-      </c>
-      <c r="AE4" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" s="5">
-        <v>1</v>
-      </c>
-      <c r="C5" s="5">
-        <v>1</v>
-      </c>
-      <c r="D5" s="5">
-        <v>1</v>
-      </c>
-      <c r="E5" s="5">
-        <v>1</v>
-      </c>
-      <c r="F5" s="5">
-        <v>1</v>
-      </c>
-      <c r="G5" s="5">
-        <v>1</v>
-      </c>
-      <c r="H5" s="5">
-        <v>1</v>
-      </c>
-      <c r="I5" s="5">
-        <v>1</v>
-      </c>
-      <c r="J5" s="5">
-        <v>1</v>
-      </c>
-      <c r="K5" s="5">
-        <v>1</v>
-      </c>
-      <c r="L5" s="5">
-        <v>1</v>
-      </c>
-      <c r="M5" s="5">
-        <v>1</v>
-      </c>
-      <c r="N5" s="5">
-        <v>1</v>
-      </c>
-      <c r="O5" s="5">
-        <v>1</v>
-      </c>
-      <c r="P5" s="5">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="5">
-        <v>1</v>
-      </c>
-      <c r="R5" s="5">
-        <v>1</v>
-      </c>
-      <c r="S5" s="5">
-        <v>1</v>
-      </c>
-      <c r="T5" s="5">
-        <v>1</v>
-      </c>
-      <c r="U5" s="5">
-        <v>1</v>
-      </c>
-      <c r="V5" s="5">
-        <v>1</v>
-      </c>
-      <c r="W5" s="5">
-        <v>1</v>
-      </c>
-      <c r="X5" s="5">
-        <v>1</v>
-      </c>
-      <c r="Y5" s="5">
-        <v>1</v>
-      </c>
-      <c r="Z5" s="5">
-        <v>1</v>
-      </c>
-      <c r="AA5" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB5" s="5">
-        <v>0</v>
-      </c>
-      <c r="AC5" s="5">
-        <v>1</v>
-      </c>
-      <c r="AD5" s="8">
-        <v>1</v>
-      </c>
-      <c r="AE5" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B6" s="3">
-        <v>1</v>
-      </c>
-      <c r="C6" s="3">
-        <v>1</v>
-      </c>
-      <c r="D6" s="3">
-        <v>1</v>
-      </c>
-      <c r="E6" s="3">
-        <v>1</v>
-      </c>
-      <c r="F6" s="3">
-        <v>1</v>
-      </c>
-      <c r="G6" s="3">
-        <v>1</v>
-      </c>
-      <c r="H6" s="3">
-        <v>1</v>
-      </c>
-      <c r="I6" s="3">
-        <v>1</v>
-      </c>
-      <c r="J6" s="3">
-        <v>1</v>
-      </c>
-      <c r="K6" s="3">
-        <v>1</v>
-      </c>
-      <c r="L6" s="3">
-        <v>1</v>
-      </c>
-      <c r="M6" s="3">
-        <v>1</v>
-      </c>
-      <c r="N6" s="3">
-        <v>1</v>
-      </c>
-      <c r="O6" s="3">
-        <v>1</v>
-      </c>
-      <c r="P6" s="3">
-        <v>1</v>
-      </c>
-      <c r="Q6" s="3">
-        <v>1</v>
-      </c>
-      <c r="R6" s="3">
-        <v>1</v>
-      </c>
-      <c r="S6" s="3">
-        <v>1</v>
-      </c>
-      <c r="T6" s="3">
-        <v>1</v>
-      </c>
-      <c r="U6" s="3">
-        <v>1</v>
-      </c>
-      <c r="V6" s="3">
-        <v>1</v>
-      </c>
-      <c r="W6" s="3">
-        <v>1</v>
-      </c>
-      <c r="X6" s="3">
-        <v>1</v>
-      </c>
-      <c r="Y6" s="3">
-        <v>1</v>
-      </c>
-      <c r="Z6" s="3">
-        <v>1</v>
-      </c>
-      <c r="AA6" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="3">
-        <v>1</v>
-      </c>
-      <c r="AD6" s="7">
-        <v>1</v>
-      </c>
-      <c r="AE6" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7" s="5">
-        <v>1</v>
-      </c>
-      <c r="C7" s="5">
-        <v>1</v>
-      </c>
-      <c r="D7" s="5">
-        <v>1</v>
-      </c>
-      <c r="E7" s="5">
-        <v>1</v>
-      </c>
-      <c r="F7" s="5">
-        <v>1</v>
-      </c>
-      <c r="G7" s="5">
-        <v>1</v>
-      </c>
-      <c r="H7" s="5">
-        <v>1</v>
-      </c>
-      <c r="I7" s="5">
-        <v>1</v>
-      </c>
-      <c r="J7" s="5">
-        <v>1</v>
-      </c>
-      <c r="K7" s="5">
-        <v>1</v>
-      </c>
-      <c r="L7" s="5">
-        <v>1</v>
-      </c>
-      <c r="M7" s="5">
-        <v>1</v>
-      </c>
-      <c r="N7" s="5">
-        <v>1</v>
-      </c>
-      <c r="O7" s="5">
-        <v>1</v>
-      </c>
-      <c r="P7" s="5">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="5">
-        <v>1</v>
-      </c>
-      <c r="R7" s="5">
-        <v>1</v>
-      </c>
-      <c r="S7" s="5">
-        <v>1</v>
-      </c>
-      <c r="T7" s="5">
-        <v>1</v>
-      </c>
-      <c r="U7" s="5">
-        <v>1</v>
-      </c>
-      <c r="V7" s="5">
-        <v>1</v>
-      </c>
-      <c r="W7" s="5">
-        <v>1</v>
-      </c>
-      <c r="X7" s="5">
-        <v>1</v>
-      </c>
-      <c r="Y7" s="5">
-        <v>1</v>
-      </c>
-      <c r="Z7" s="5">
-        <v>1</v>
-      </c>
-      <c r="AA7" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="5">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="5">
-        <v>1</v>
-      </c>
-      <c r="AD7" s="8">
-        <v>1</v>
-      </c>
-      <c r="AE7" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>32</v>
-      </c>
       <c r="B8" s="3">
         <v>1</v>
       </c>
@@ -2133,14 +2116,14 @@
       <c r="AC8" s="3">
         <v>1</v>
       </c>
-      <c r="AD8" s="7">
-        <v>1</v>
-      </c>
-      <c r="AE8" s="7">
+      <c r="AD8" s="3">
+        <v>1</v>
+      </c>
+      <c r="AE8" s="3">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>